--- a/outputs_district/manuscript_tables.xlsx
+++ b/outputs_district/manuscript_tables.xlsx
@@ -21,13 +21,14 @@
     <sheet name="Ablation" sheetId="12" r:id="rId12"/>
     <sheet name="Tier 3 coverage" sheetId="13" r:id="rId13"/>
     <sheet name="Top recommendations" sheetId="14" r:id="rId14"/>
+    <sheet name="Population proxy" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="232">
   <si>
     <t>ID</t>
   </si>
@@ -110,6 +111,9 @@
     <t>F22</t>
   </si>
   <si>
+    <t>F5-shared</t>
+  </si>
+  <si>
     <t>Min–Max normalisation</t>
   </si>
   <si>
@@ -176,6 +180,9 @@
     <t>Hard eligibility gates</t>
   </si>
   <si>
+    <t>Common-scale rescale (ablation classification only)</t>
+  </si>
+  <si>
     <t>x'ᵢ = (xᵢ − x_min)/(x_max − x_min)</t>
   </si>
   <si>
@@ -242,6 +249,9 @@
     <t>ineligible if d_coast &lt; 50 m OR any hazard class = 3</t>
   </si>
   <si>
+    <t>S'ᵢ = (Sᵢ − S_min^B)/(S_max^B − S_min^B), both configurations</t>
+  </si>
+  <si>
     <t>Min–Max Normalization</t>
   </si>
   <si>
@@ -281,6 +291,9 @@
     <t>Hard Eligibility Gates</t>
   </si>
   <si>
+    <t>Baseline Score Rescaling (post-run correction)</t>
+  </si>
+  <si>
     <t>f1_minmax</t>
   </si>
   <si>
@@ -347,6 +360,9 @@
     <t>f22_eligibility</t>
   </si>
   <si>
+    <t>f5_shared_rescale</t>
+  </si>
+  <si>
     <t>barangay</t>
   </si>
   <si>
@@ -410,13 +426,13 @@
     <t>74-A Matina Crossing</t>
   </si>
   <si>
-    <t>Talomo River</t>
+    <t>Talomo Proper</t>
   </si>
   <si>
     <t>exact</t>
   </si>
   <si>
-    <t>containment</t>
+    <t>alias</t>
   </si>
   <si>
     <t>Barangay</t>
@@ -641,13 +657,13 @@
     <t>Buffer (km)</t>
   </si>
   <si>
-    <t>polaris_pct</t>
-  </si>
-  <si>
     <t>current_pct</t>
   </si>
   <si>
-    <t>delta_pct</t>
+    <t>combined_pct</t>
+  </si>
+  <si>
+    <t>marginal_gain_pct</t>
   </si>
   <si>
     <t>recommendation_rank</t>
@@ -674,22 +690,40 @@
     <t>recommendation_eligible</t>
   </si>
   <si>
-    <t>TALOMO_1133</t>
-  </si>
-  <si>
-    <t>TALOMO_0305</t>
-  </si>
-  <si>
-    <t>TALOMO_1009</t>
-  </si>
-  <si>
-    <t>Few buildings surround this site (7 within 300 m), so demand here is likely low. Road access is strong — about 2 m to the nearest road. The nearest existing health facility is about 2,452 m away, so this area is currently underserved. No flood, landslide or storm-surge hazard is mapped here.</t>
-  </si>
-  <si>
-    <t>Few buildings surround this site (180 within 300 m), so demand here is likely low. Road access is strong — about 1 m to the nearest road. An existing health facility is already about 404 m away. No flood, landslide or storm-surge hazard is mapped here.</t>
-  </si>
-  <si>
-    <t>Few buildings surround this site (0 within 300 m), so demand here is likely low. Road access is strong — about 1 m to the nearest road. The nearest existing health facility is about 1,797 m away, so this area is currently underserved. No flood, landslide or storm-surge hazard is mapped here.</t>
+    <t>TALOMO_0765</t>
+  </si>
+  <si>
+    <t>TALOMO_1137</t>
+  </si>
+  <si>
+    <t>TALOMO_1179</t>
+  </si>
+  <si>
+    <t>Few buildings surround this site (153 within 300 m), so demand here is likely low. Road access is strong — about 2 m to the nearest road. An existing health facility is already about 703 m away. No flood, landslide or storm-surge hazard is mapped here.</t>
+  </si>
+  <si>
+    <t>The surrounding area is moderately built up (631 buildings within 300 m). Road access is moderate, roughly 7 m to the nearest road. An existing health facility is already about 644 m away. No flood, landslide or storm-surge hazard is mapped here.</t>
+  </si>
+  <si>
+    <t>The surrounding area is moderately built up (723 buildings within 300 m). Road access is weak — about 16 m to the nearest road. An existing health facility is already about 882 m away. No flood, landslide or storm-surge hazard is mapped here.</t>
+  </si>
+  <si>
+    <t>PSA_2024_Population</t>
+  </si>
+  <si>
+    <t>Building_Footprints</t>
+  </si>
+  <si>
+    <t>Persons_per_Footprint</t>
+  </si>
+  <si>
+    <t>Proxy_Implied_Population</t>
+  </si>
+  <si>
+    <t>Signed_Deviation_Pct</t>
+  </si>
+  <si>
+    <t>Abs_Deviation_Pct</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1072,16 +1106,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1089,16 +1123,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1106,16 +1140,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1123,16 +1157,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1140,16 +1174,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1157,16 +1191,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1174,16 +1208,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1191,16 +1225,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1208,16 +1242,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1225,16 +1259,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1242,16 +1276,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1259,16 +1293,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1276,16 +1310,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1293,16 +1327,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1310,16 +1344,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1327,16 +1361,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1344,16 +1378,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1361,16 +1395,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1378,16 +1412,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1395,16 +1429,16 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1412,16 +1446,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1429,16 +1463,33 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1453,70 +1504,70 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B2">
-        <v>1304</v>
+        <v>1278</v>
       </c>
       <c r="C2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B3">
-        <v>1322</v>
+        <v>1266</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B4">
-        <v>1340</v>
+        <v>1244</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E4">
-        <v>140</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1531,42 +1582,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B3">
-        <v>230</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B4">
-        <v>236</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B5">
-        <v>1299</v>
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -1581,63 +1632,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B2">
-        <v>0.779355430014142</v>
+        <v>0.7366259876793413</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B3">
-        <v>73.68078175895765</v>
+        <v>27.43009320905459</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B4">
-        <v>0.01933984799131379</v>
+        <v>0.02223035952063915</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B5">
-        <v>0.4285714285714285</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B7">
-        <v>0.7391304347826086</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>0.5873015873015873</v>
@@ -1655,16 +1706,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1672,13 +1723,13 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>89.25238940727588</v>
+        <v>99.35045653626308</v>
       </c>
       <c r="C2">
-        <v>99.3048997015602</v>
+        <v>99.8589562764457</v>
       </c>
       <c r="D2">
-        <v>-10.05251029428432</v>
+        <v>0.5084997401826143</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1686,13 +1737,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>98.83646254391599</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>-1.163537456084015</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1707,31 +1758,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1739,25 +1790,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C2">
-        <v>0.82</v>
+        <v>0.8228</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E2">
-        <v>7.1026</v>
+        <v>7.073</v>
       </c>
       <c r="F2">
-        <v>125.5313</v>
+        <v>125.5666</v>
       </c>
       <c r="G2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -1768,25 +1819,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C3">
-        <v>0.8168</v>
+        <v>0.8053</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E3">
-        <v>7.0529</v>
+        <v>7.0955</v>
       </c>
       <c r="F3">
-        <v>125.5152</v>
+        <v>125.5781</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -1797,28 +1848,383 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C4">
-        <v>0.8077</v>
+        <v>0.7963</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E4">
-        <v>7.0958</v>
+        <v>7.0978</v>
       </c>
       <c r="F4">
-        <v>125.5313</v>
+        <v>125.5781</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2">
+        <v>18515</v>
+      </c>
+      <c r="C2">
+        <v>399</v>
+      </c>
+      <c r="D2">
+        <v>46.4</v>
+      </c>
+      <c r="E2">
+        <v>8254</v>
+      </c>
+      <c r="F2">
+        <v>-55.42</v>
+      </c>
+      <c r="G2">
+        <v>55.42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3">
+        <v>21409</v>
+      </c>
+      <c r="C3">
+        <v>342</v>
+      </c>
+      <c r="D3">
+        <v>62.6</v>
+      </c>
+      <c r="E3">
+        <v>7075</v>
+      </c>
+      <c r="F3">
+        <v>-66.95</v>
+      </c>
+      <c r="G3">
+        <v>66.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4">
+        <v>18118</v>
+      </c>
+      <c r="C4">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>549.03</v>
+      </c>
+      <c r="E4">
+        <v>683</v>
+      </c>
+      <c r="F4">
+        <v>-96.23</v>
+      </c>
+      <c r="G4">
+        <v>96.23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5">
+        <v>83192</v>
+      </c>
+      <c r="C5">
+        <v>4644</v>
+      </c>
+      <c r="D5">
+        <v>17.91</v>
+      </c>
+      <c r="E5">
+        <v>96070</v>
+      </c>
+      <c r="F5">
+        <v>15.48</v>
+      </c>
+      <c r="G5">
+        <v>15.48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6">
+        <v>42868</v>
+      </c>
+      <c r="C6">
+        <v>1465</v>
+      </c>
+      <c r="D6">
+        <v>29.26</v>
+      </c>
+      <c r="E6">
+        <v>30306</v>
+      </c>
+      <c r="F6">
+        <v>-29.3</v>
+      </c>
+      <c r="G6">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7">
+        <v>29445</v>
+      </c>
+      <c r="C7">
+        <v>149</v>
+      </c>
+      <c r="D7">
+        <v>197.62</v>
+      </c>
+      <c r="E7">
+        <v>3082</v>
+      </c>
+      <c r="F7">
+        <v>-89.53</v>
+      </c>
+      <c r="G7">
+        <v>89.53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8">
+        <v>21900</v>
+      </c>
+      <c r="C8">
+        <v>122</v>
+      </c>
+      <c r="D8">
+        <v>179.51</v>
+      </c>
+      <c r="E8">
+        <v>2524</v>
+      </c>
+      <c r="F8">
+        <v>-88.47</v>
+      </c>
+      <c r="G8">
+        <v>88.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9">
+        <v>4597</v>
+      </c>
+      <c r="C9">
+        <v>65</v>
+      </c>
+      <c r="D9">
+        <v>70.72</v>
+      </c>
+      <c r="E9">
+        <v>1345</v>
+      </c>
+      <c r="F9">
+        <v>-70.73999999999999</v>
+      </c>
+      <c r="G9">
+        <v>70.73999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10">
+        <v>61565</v>
+      </c>
+      <c r="C10">
+        <v>6364</v>
+      </c>
+      <c r="D10">
+        <v>9.67</v>
+      </c>
+      <c r="E10">
+        <v>131651</v>
+      </c>
+      <c r="F10">
+        <v>113.84</v>
+      </c>
+      <c r="G10">
+        <v>113.84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11">
+        <v>5220</v>
+      </c>
+      <c r="C11">
+        <v>266</v>
+      </c>
+      <c r="D11">
+        <v>19.62</v>
+      </c>
+      <c r="E11">
+        <v>5503</v>
+      </c>
+      <c r="F11">
+        <v>5.42</v>
+      </c>
+      <c r="G11">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12">
+        <v>33531</v>
+      </c>
+      <c r="C12">
+        <v>2167</v>
+      </c>
+      <c r="D12">
+        <v>15.47</v>
+      </c>
+      <c r="E12">
+        <v>44828</v>
+      </c>
+      <c r="F12">
+        <v>33.69</v>
+      </c>
+      <c r="G12">
+        <v>33.69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13">
+        <v>39797</v>
+      </c>
+      <c r="C13">
+        <v>4220</v>
+      </c>
+      <c r="D13">
+        <v>9.43</v>
+      </c>
+      <c r="E13">
+        <v>87299</v>
+      </c>
+      <c r="F13">
+        <v>119.36</v>
+      </c>
+      <c r="G13">
+        <v>119.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14">
+        <v>22277</v>
+      </c>
+      <c r="C14">
+        <v>1091</v>
+      </c>
+      <c r="D14">
+        <v>20.42</v>
+      </c>
+      <c r="E14">
+        <v>22569</v>
+      </c>
+      <c r="F14">
+        <v>1.31</v>
+      </c>
+      <c r="G14">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15">
+        <v>65379</v>
+      </c>
+      <c r="C15">
+        <v>1287</v>
+      </c>
+      <c r="D15">
+        <v>50.8</v>
+      </c>
+      <c r="E15">
+        <v>26624</v>
+      </c>
+      <c r="F15">
+        <v>-59.28</v>
+      </c>
+      <c r="G15">
+        <v>59.28</v>
       </c>
     </row>
   </sheetData>
@@ -1833,27 +2239,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D2">
         <v>2.193168302470114</v>
@@ -1861,13 +2267,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D3">
         <v>9.148050380769511</v>
@@ -1875,13 +2281,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4">
         <v>2.615961821948404</v>
@@ -1889,13 +2295,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D5">
         <v>4.602254964819464</v>
@@ -1903,13 +2309,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D6">
         <v>15.60335044573281</v>
@@ -1917,13 +2323,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D7">
         <v>6.6142861813373</v>
@@ -1931,13 +2337,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D8">
         <v>5.268410538156965</v>
@@ -1945,13 +2351,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D9">
         <v>9.429965403558237</v>
@@ -1959,13 +2365,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D10">
         <v>10.43000993974171</v>
@@ -1973,13 +2379,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D11">
         <v>6.890898087491975</v>
@@ -1987,13 +2393,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D12">
         <v>3.417950928296884</v>
@@ -2001,13 +2407,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D13">
         <v>4.907035667208568</v>
@@ -2015,13 +2421,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D14">
         <v>5.881873431683787</v>
@@ -2029,16 +2435,16 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D15">
-        <v>8.872503354555748</v>
+        <v>6.453434111476941</v>
       </c>
     </row>
   </sheetData>
@@ -2053,63 +2459,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B3">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B5">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B6">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B7">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B8">
         <v>86</v>
@@ -2117,39 +2523,39 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B9">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B10">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B11">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B12">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B13">
         <v>79</v>
@@ -2157,18 +2563,18 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B14">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B15">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2183,45 +2589,45 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B2">
-        <v>1535</v>
+        <v>1502</v>
       </c>
       <c r="C2">
-        <v>63.57785016286645</v>
+        <v>68.85752330226364</v>
       </c>
       <c r="D2">
-        <v>126.7142748948551</v>
+        <v>129.3918525474233</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -2230,100 +2636,100 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>64</v>
+        <v>75.5</v>
       </c>
       <c r="I2">
-        <v>1133</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B3">
-        <v>1535</v>
+        <v>1502</v>
       </c>
       <c r="C3">
-        <v>110.1045432363171</v>
+        <v>107.7350457701619</v>
       </c>
       <c r="D3">
-        <v>109.3617188633597</v>
+        <v>111.0365322529405</v>
       </c>
       <c r="E3">
-        <v>1.336912122390081</v>
+        <v>1.299426419506374</v>
       </c>
       <c r="F3">
-        <v>31.81673756868439</v>
+        <v>29.78803621881513</v>
       </c>
       <c r="G3">
-        <v>70.82676306606059</v>
+        <v>67.5065317762043</v>
       </c>
       <c r="H3">
-        <v>152.8315262546302</v>
+        <v>149.2671802247507</v>
       </c>
       <c r="I3">
-        <v>727.6806324223202</v>
+        <v>673.8561792251329</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B4">
-        <v>1535</v>
+        <v>1502</v>
       </c>
       <c r="C4">
-        <v>1003.318484713668</v>
+        <v>977.3618951383884</v>
       </c>
       <c r="D4">
-        <v>675.8457637347666</v>
+        <v>679.2657833396286</v>
       </c>
       <c r="E4">
-        <v>22.61866037276938</v>
+        <v>6.569811427033954</v>
       </c>
       <c r="F4">
-        <v>531.4222968028774</v>
+        <v>506.3764202478369</v>
       </c>
       <c r="G4">
-        <v>873.3022293441305</v>
+        <v>836.0586729084596</v>
       </c>
       <c r="H4">
-        <v>1263.678429619144</v>
+        <v>1221.58572795991</v>
       </c>
       <c r="I4">
-        <v>3967.693794584598</v>
+        <v>3960.270604484194</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B5">
-        <v>1535</v>
+        <v>1502</v>
       </c>
       <c r="C5">
-        <v>5307.322177449601</v>
+        <v>3807.530646664178</v>
       </c>
       <c r="D5">
-        <v>4683.314863812931</v>
+        <v>2456.777605154063</v>
       </c>
       <c r="E5">
-        <v>7.565819017289766</v>
+        <v>5.425364111897423</v>
       </c>
       <c r="F5">
-        <v>2305.642835367687</v>
+        <v>1754.252567272349</v>
       </c>
       <c r="G5">
-        <v>4140.919387730015</v>
+        <v>3602.34800797974</v>
       </c>
       <c r="H5">
-        <v>6489.676299918231</v>
+        <v>5545.4569736378</v>
       </c>
       <c r="I5">
-        <v>19907.74740642393</v>
+        <v>10474.88318426248</v>
       </c>
     </row>
   </sheetData>
@@ -2338,34 +2744,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2379,22 +2785,22 @@
         <v>500</v>
       </c>
       <c r="E2">
-        <v>0.0134151341670842</v>
+        <v>0.0144327305243183</v>
       </c>
       <c r="F2">
-        <v>0.000730521146132</v>
+        <v>0.0016213039783835</v>
       </c>
       <c r="G2">
-        <v>0.0244436723894403</v>
+        <v>0.02562536740517</v>
       </c>
       <c r="H2">
-        <v>0.0014429388627054</v>
+        <v>0.0039609164317593</v>
       </c>
       <c r="I2">
-        <v>0.9492674012310872</v>
+        <v>0.9432875056530092</v>
       </c>
       <c r="J2">
-        <v>0.0055622516878765</v>
+        <v>0.0156841657132434</v>
       </c>
     </row>
   </sheetData>
@@ -2409,58 +2815,58 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B2">
-        <v>0.01196128558490827</v>
+        <v>0.01295950958524004</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B3">
-        <v>0.02252142332207471</v>
+        <v>0.02039673983005129</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B4">
-        <v>0.9634666315052178</v>
+        <v>0.9638594478655601</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B5">
-        <v>0.9548174736971631</v>
+        <v>0.9470882172175662</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B6">
-        <v>0.9492674012310871</v>
+        <v>0.9432875056530092</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B7">
-        <v>0.005562251687876518</v>
+        <v>0.01568416571324349</v>
       </c>
     </row>
   </sheetData>
@@ -2475,121 +2881,121 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>0.4</v>
       </c>
       <c r="C2">
-        <v>0.4547218617662322</v>
+        <v>0.4069187383882709</v>
       </c>
       <c r="D2">
-        <v>0.01144422292001207</v>
+        <v>0.008310746633132939</v>
       </c>
       <c r="E2">
-        <v>0.0008181973807374867</v>
+        <v>0.0008697161113705956</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B3">
         <v>0.25</v>
       </c>
       <c r="C3">
-        <v>0.2134059533520917</v>
+        <v>0.2055063321344571</v>
       </c>
       <c r="D3">
-        <v>0.006679280665997806</v>
+        <v>0.006341603591853475</v>
       </c>
       <c r="E3">
-        <v>0.0005129732520118165</v>
+        <v>0.0004514107186242843</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B4">
         <v>0.15</v>
       </c>
       <c r="C4">
-        <v>0.1405949318031899</v>
+        <v>0.1442361586130013</v>
       </c>
       <c r="D4">
-        <v>0.003892391117566537</v>
+        <v>0.005482973485938467</v>
       </c>
       <c r="E4">
-        <v>9.117153931150633E-05</v>
+        <v>0.000353026528011652</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B5">
         <v>0.08</v>
       </c>
       <c r="C5">
-        <v>0.0888253014280226</v>
+        <v>0.1144393739306622</v>
       </c>
       <c r="D5">
-        <v>0.003230981725386636</v>
+        <v>0.002498327528536032</v>
       </c>
       <c r="E5">
-        <v>0.0003787212769069592</v>
+        <v>0.0001625588038078075</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B6">
         <v>0.07000000000000001</v>
       </c>
       <c r="C6">
-        <v>0.0564567900734527</v>
+        <v>0.07003306303242793</v>
       </c>
       <c r="D6">
-        <v>0.001222086176990187</v>
+        <v>0.002252911430840109</v>
       </c>
       <c r="E6">
-        <v>7.601674826503712E-05</v>
+        <v>0.0001552703360623234</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B7">
         <v>0.05</v>
       </c>
       <c r="C7">
-        <v>0.0459951615770109</v>
+        <v>0.05886633390118055</v>
       </c>
       <c r="D7">
-        <v>0.001064449879582337</v>
+        <v>0.00178086096490927</v>
       </c>
       <c r="E7">
-        <v>5.741875300807103E-05</v>
+        <v>0.0001354126668069689</v>
       </c>
     </row>
   </sheetData>
@@ -2604,27 +3010,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B2">
-        <v>1.80684247163381E-16</v>
+        <v>8.335986636237543E-17</v>
       </c>
       <c r="C2">
-        <v>2.965369665759676E-16</v>
+        <v>1.067850942561339E-16</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2632,16 +3038,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B3">
-        <v>0.01196128558490827</v>
+        <v>0.01295950958524004</v>
       </c>
       <c r="C3">
-        <v>0.02252142332207471</v>
+        <v>0.02039673983005129</v>
       </c>
       <c r="D3">
-        <v>0.9634666315052178</v>
+        <v>0.9638594478655601</v>
       </c>
     </row>
   </sheetData>
@@ -2656,57 +3062,57 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C2">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B3">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="C3">
-        <v>15.18</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B4">
-        <v>974</v>
+        <v>919</v>
       </c>
       <c r="C4">
-        <v>63.45</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B5">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="C5">
-        <v>19.48</v>
+        <v>15.98</v>
       </c>
     </row>
   </sheetData>
